--- a/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
+++ b/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
@@ -10,17 +10,16 @@
     <sheet name="VanWestendorp" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="GaborGranger" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Monadic" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Simulator" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Validation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Reference" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Insights" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="AddedSlides" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Validation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Reference" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Insights" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AddedSlides" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="280">
   <si>
     <t xml:space="preserve">TURAS Pricing Module - Configuration</t>
   </si>
@@ -689,63 +688,6 @@
   </si>
   <si>
     <t xml:space="preserve">50 to 500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pricing Simulator - Preset Scenarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define preset scenarios for the interactive simulator dashboard. Each row becomes a clickable scenario card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product_Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competitor_1_Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competitor_2_Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Competitor_3_Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Display name for this scenario preset (e.g., 'Budget Launcher', 'Premium Pro').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Product price for this scenario.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Competitor 1 price. Leave blank if not applicable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Competitor 2 price. Leave blank if not applicable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Competitor 3 price. Leave blank if not applicable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] Brief description shown on scenario card in the simulator.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Example] Budget Launcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aggressive entry-level pricing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Example] Market Match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price parity with main competitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Example] Premium Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium positioning with value story</t>
   </si>
   <si>
     <t xml:space="preserve">Data Quality &amp; Validation Settings</t>
@@ -924,7 +866,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -994,13 +936,8 @@
       <color rgb="FF388E3C"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF37474F"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1040,11 +977,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F9FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F2FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -1088,7 +1020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1135,9 +1067,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3231,225 +3160,6 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="18.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B5" s="17" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>16.99</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <v>12.99</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="B5:B17">
-      <formula1>0</formula1>
-      <formula2>999999</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
     <col min="1" max="1" width="38.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
@@ -3459,12 +3169,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -3503,7 +3213,7 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -3512,24 +3222,24 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>216</v>
@@ -3538,44 +3248,44 @@
         <v>4</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3607,7 +3317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3618,23 +3328,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
@@ -3642,7 +3352,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
@@ -3650,7 +3360,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -3658,7 +3368,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
@@ -3666,15 +3376,15 @@
         <v>23</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -3682,7 +3392,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -3690,7 +3400,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -3698,15 +3408,15 @@
         <v>23</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
@@ -3714,7 +3424,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
@@ -3722,7 +3432,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
@@ -3730,15 +3440,15 @@
         <v>23</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18">
@@ -3746,7 +3456,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19">
@@ -3754,7 +3464,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20">
@@ -3762,7 +3472,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21">
@@ -3770,7 +3480,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3782,22 +3492,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>23</v>
@@ -3813,7 +3523,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
@@ -3821,7 +3531,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>23</v>
@@ -3829,7 +3539,7 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>23</v>
@@ -3837,7 +3547,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>23</v>
@@ -3845,7 +3555,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>23</v>
@@ -3857,7 +3567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3870,24 +3580,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>23</v>

--- a/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
+++ b/modules/pricing/docs/templates/Pricing_Config_Template.xlsx
@@ -222,7 +222,7 @@
     <t xml:space="preserve">Export_WTP</t>
   </si>
   <si>
-    <t xml:space="preserve">Also export a per-respondent willingness-to-pay column (midpoint of the Van Westendorp cheap and expensive answers), stamped as derived on the METHOD sheet. Not built yet: Y refuses until the pricing v2 session lands.</t>
+    <t xml:space="preserve">Also export a per-respondent willingness-to-pay column as a Numeric question: the highest Gabor-Granger price accepted when the ladder ran (capped at the top of the ladder), otherwise the midpoint of the Van Westendorp cheap and expensive answers, stamped as derived on the METHOD sheet. Written to the same {output}_tabs_pricing.xlsx. Needs ID_Variable.</t>
   </si>
   <si>
     <t xml:space="preserve">MONOTONICITY HANDLING</t>
